--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,6 +1171,1364 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120253032</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90582</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579906</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406381</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120253290</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580176</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6406245</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120253308</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6406230</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120252861</v>
+      </c>
+      <c r="B9" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579924</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6406344</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120253384</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580279</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6406123</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120252820</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579928</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6406349</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120253744</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580170</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6406337</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120253417</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90966</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>580291</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6406128</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120253365</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580255</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6406137</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120253238</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>580237</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6406426</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120253569</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91836</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579980</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6406368</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120253451</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 42738, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6406118</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253032</v>
+        <v>120253290</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,12 +1211,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,13 +1225,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579906</v>
+        <v>580176</v>
       </c>
       <c r="R6" t="n">
-        <v>6406381</v>
+        <v>6406245</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1269,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253290</v>
+        <v>120253365</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,39 +1299,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580176</v>
+        <v>580255</v>
       </c>
       <c r="R7" t="n">
-        <v>6406245</v>
+        <v>6406137</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,6 +1383,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1404,7 +1405,7 @@
         <v>120253308</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1515,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120252861</v>
+        <v>120253569</v>
       </c>
       <c r="B9" t="n">
-        <v>94681</v>
+        <v>91854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,27 +1532,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1559,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579924</v>
+        <v>579980</v>
       </c>
       <c r="R9" t="n">
-        <v>6406344</v>
+        <v>6406368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,17 +1623,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253384</v>
+        <v>120253032</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,35 +1642,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580279</v>
+        <v>579906</v>
       </c>
       <c r="R10" t="n">
-        <v>6406123</v>
+        <v>6406381</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,17 +1737,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120252820</v>
+        <v>120253417</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>90984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,30 +1756,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1784,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579928</v>
+        <v>580291</v>
       </c>
       <c r="R11" t="n">
-        <v>6406349</v>
+        <v>6406128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,17 +1851,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253744</v>
+        <v>120253238</v>
       </c>
       <c r="B12" t="n">
-        <v>96862</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,35 +1870,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1899,13 +1910,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580170</v>
+        <v>580237</v>
       </c>
       <c r="R12" t="n">
-        <v>6406337</v>
+        <v>6406426</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1937,17 +1948,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253417</v>
+        <v>120253384</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,38 +1985,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580291</v>
+        <v>580279</v>
       </c>
       <c r="R13" t="n">
-        <v>6406128</v>
+        <v>6406123</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253365</v>
+        <v>120253744</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>96885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,35 +2096,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2132,13 +2136,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580255</v>
+        <v>580170</v>
       </c>
       <c r="R14" t="n">
-        <v>6406137</v>
+        <v>6406337</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,13 +2174,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2188,17 +2196,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120253238</v>
+        <v>120253451</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>94704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,37 +2215,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580237</v>
+        <v>580200</v>
       </c>
       <c r="R15" t="n">
-        <v>6406426</v>
+        <v>6406118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,17 +2303,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120253569</v>
+        <v>120252820</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>91902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,35 +2322,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4363</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579980</v>
+        <v>579928</v>
       </c>
       <c r="R16" t="n">
-        <v>6406368</v>
+        <v>6406349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120253451</v>
+        <v>120252861</v>
       </c>
       <c r="B17" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580200</v>
+        <v>579924</v>
       </c>
       <c r="R17" t="n">
-        <v>6406118</v>
+        <v>6406344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253365</v>
+        <v>120253308</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,39 +1299,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580255</v>
+        <v>580160</v>
       </c>
       <c r="R7" t="n">
-        <v>6406137</v>
+        <v>6406230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253308</v>
+        <v>120253569</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,21 +1417,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1442,7 +1441,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1453,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580160</v>
+        <v>579980</v>
       </c>
       <c r="R8" t="n">
-        <v>6406230</v>
+        <v>6406368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253569</v>
+        <v>120253365</v>
       </c>
       <c r="B9" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,38 +1527,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579980</v>
+        <v>580255</v>
       </c>
       <c r="R9" t="n">
-        <v>6406368</v>
+        <v>6406137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253384</v>
+        <v>120253744</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,31 +1985,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2021,13 +2025,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580279</v>
+        <v>580170</v>
       </c>
       <c r="R13" t="n">
-        <v>6406123</v>
+        <v>6406337</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,13 +2063,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2077,17 +2085,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253744</v>
+        <v>120253384</v>
       </c>
       <c r="B14" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,35 +2104,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2136,13 +2140,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580170</v>
+        <v>580279</v>
       </c>
       <c r="R14" t="n">
-        <v>6406337</v>
+        <v>6406123</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2174,17 +2178,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253290</v>
+        <v>120253032</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,13 +1211,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580176</v>
+        <v>579906</v>
       </c>
       <c r="R6" t="n">
-        <v>6406245</v>
+        <v>6406381</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,6 +1268,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253308</v>
+        <v>120253238</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,38 +1299,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1338,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580160</v>
+        <v>580237</v>
       </c>
       <c r="R7" t="n">
-        <v>6406230</v>
+        <v>6406426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,17 +1395,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253569</v>
+        <v>120253290</v>
       </c>
       <c r="B8" t="n">
-        <v>91854</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,25 +1414,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1439,12 +1440,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1452,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579980</v>
+        <v>580176</v>
       </c>
       <c r="R8" t="n">
-        <v>6406368</v>
+        <v>6406245</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1498,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1515,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253365</v>
+        <v>120252861</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,37 +1528,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1567,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580255</v>
+        <v>579924</v>
       </c>
       <c r="R9" t="n">
-        <v>6406137</v>
+        <v>6406344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,17 +1616,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253032</v>
+        <v>120253744</v>
       </c>
       <c r="B10" t="n">
-        <v>90600</v>
+        <v>96885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,38 +1635,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1681,13 +1675,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579906</v>
+        <v>580170</v>
       </c>
       <c r="R10" t="n">
-        <v>6406381</v>
+        <v>6406337</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,13 +1713,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1856,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253238</v>
+        <v>120253384</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1891,11 +1889,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1910,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580237</v>
+        <v>580279</v>
       </c>
       <c r="R12" t="n">
-        <v>6406426</v>
+        <v>6406123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,17 +1960,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253744</v>
+        <v>120253308</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,35 +1983,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2025,13 +2018,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580170</v>
+        <v>580160</v>
       </c>
       <c r="R13" t="n">
-        <v>6406337</v>
+        <v>6406230</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,17 +2056,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2085,17 +2074,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253384</v>
+        <v>120252820</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,35 +2093,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2140,10 +2132,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580279</v>
+        <v>579928</v>
       </c>
       <c r="R14" t="n">
-        <v>6406123</v>
+        <v>6406349</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,17 +2188,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120253451</v>
+        <v>120253365</v>
       </c>
       <c r="B15" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,29 +2207,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580200</v>
+        <v>580255</v>
       </c>
       <c r="R15" t="n">
-        <v>6406118</v>
+        <v>6406137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120252820</v>
+        <v>120253569</v>
       </c>
       <c r="B16" t="n">
-        <v>91902</v>
+        <v>91854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,35 +2322,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579928</v>
+        <v>579980</v>
       </c>
       <c r="R16" t="n">
-        <v>6406349</v>
+        <v>6406368</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,14 +2417,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120252861</v>
+        <v>120253451</v>
       </c>
       <c r="B17" t="n">
         <v>94704</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579924</v>
+        <v>580200</v>
       </c>
       <c r="R17" t="n">
-        <v>6406344</v>
+        <v>6406118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253032</v>
+        <v>120253238</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,38 +1185,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579906</v>
+        <v>580237</v>
       </c>
       <c r="R6" t="n">
-        <v>6406381</v>
+        <v>6406426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253238</v>
+        <v>120253032</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,39 +1300,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580237</v>
+        <v>579906</v>
       </c>
       <c r="R7" t="n">
-        <v>6406426</v>
+        <v>6406381</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253290</v>
+        <v>120252861</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,39 +1414,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1454,13 +1446,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580176</v>
+        <v>579924</v>
       </c>
       <c r="R8" t="n">
-        <v>6406245</v>
+        <v>6406344</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,6 +1490,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1509,17 +1502,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120252861</v>
+        <v>120253290</v>
       </c>
       <c r="B9" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,31 +1521,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1560,13 +1561,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579924</v>
+        <v>580176</v>
       </c>
       <c r="R9" t="n">
-        <v>6406344</v>
+        <v>6406245</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,7 +1605,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253238</v>
+        <v>120253290</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,39 +1185,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580237</v>
+        <v>580176</v>
       </c>
       <c r="R6" t="n">
-        <v>6406426</v>
+        <v>6406245</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,7 +1269,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1281,17 +1280,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253032</v>
+        <v>120253451</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,38 +1299,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579906</v>
+        <v>580200</v>
       </c>
       <c r="R7" t="n">
-        <v>6406381</v>
+        <v>6406118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,17 +1387,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120252861</v>
+        <v>120253032</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,31 +1406,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579924</v>
+        <v>579906</v>
       </c>
       <c r="R8" t="n">
-        <v>6406344</v>
+        <v>6406381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1509,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253290</v>
+        <v>120253365</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,39 +1520,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1561,13 +1560,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580176</v>
+        <v>580255</v>
       </c>
       <c r="R9" t="n">
-        <v>6406245</v>
+        <v>6406137</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253417</v>
+        <v>120253308</v>
       </c>
       <c r="B11" t="n">
-        <v>90984</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580291</v>
+        <v>580160</v>
       </c>
       <c r="R11" t="n">
-        <v>6406128</v>
+        <v>6406230</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253384</v>
+        <v>120253569</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,35 +1868,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1904,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580279</v>
+        <v>579980</v>
       </c>
       <c r="R12" t="n">
-        <v>6406123</v>
+        <v>6406368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1967,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253308</v>
+        <v>120253238</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,38 +1982,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,10 +2022,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580160</v>
+        <v>580237</v>
       </c>
       <c r="R13" t="n">
-        <v>6406230</v>
+        <v>6406426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,17 +2078,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120252820</v>
+        <v>120253417</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>90984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,30 +2097,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579928</v>
+        <v>580291</v>
       </c>
       <c r="R14" t="n">
-        <v>6406349</v>
+        <v>6406128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,17 +2192,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120253365</v>
+        <v>120252820</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,39 +2211,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2247,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580255</v>
+        <v>579928</v>
       </c>
       <c r="R15" t="n">
-        <v>6406137</v>
+        <v>6406349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,17 +2306,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120253569</v>
+        <v>120252861</v>
       </c>
       <c r="B16" t="n">
-        <v>91854</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,34 +2329,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2361,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579980</v>
+        <v>579924</v>
       </c>
       <c r="R16" t="n">
-        <v>6406368</v>
+        <v>6406344</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,17 +2413,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120253451</v>
+        <v>120253384</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,29 +2432,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580200</v>
+        <v>580279</v>
       </c>
       <c r="R17" t="n">
-        <v>6406118</v>
+        <v>6406123</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253290</v>
+        <v>120253032</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,13 +1211,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580176</v>
+        <v>579906</v>
       </c>
       <c r="R6" t="n">
-        <v>6406245</v>
+        <v>6406381</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,6 +1268,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253451</v>
+        <v>120253308</v>
       </c>
       <c r="B7" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,27 +1303,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1331,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580200</v>
+        <v>580160</v>
       </c>
       <c r="R7" t="n">
-        <v>6406118</v>
+        <v>6406230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253032</v>
+        <v>120253451</v>
       </c>
       <c r="B8" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,38 +1413,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579906</v>
+        <v>580200</v>
       </c>
       <c r="R8" t="n">
-        <v>6406381</v>
+        <v>6406118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253308</v>
+        <v>120253417</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>90984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580160</v>
+        <v>580291</v>
       </c>
       <c r="R11" t="n">
-        <v>6406230</v>
+        <v>6406128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253569</v>
+        <v>120253238</v>
       </c>
       <c r="B12" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,38 +1868,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1907,10 +1908,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579980</v>
+        <v>580237</v>
       </c>
       <c r="R12" t="n">
-        <v>6406368</v>
+        <v>6406426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1963,17 +1964,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253238</v>
+        <v>120253290</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,39 +1983,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2022,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580237</v>
+        <v>580176</v>
       </c>
       <c r="R13" t="n">
-        <v>6406426</v>
+        <v>6406245</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,7 +2067,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2078,17 +2078,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253417</v>
+        <v>120253384</v>
       </c>
       <c r="B14" t="n">
-        <v>90984</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,38 +2097,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2136,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580291</v>
+        <v>580279</v>
       </c>
       <c r="R14" t="n">
-        <v>6406128</v>
+        <v>6406123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120252861</v>
+        <v>120253569</v>
       </c>
       <c r="B16" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,27 +2326,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2357,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579924</v>
+        <v>579980</v>
       </c>
       <c r="R16" t="n">
-        <v>6406344</v>
+        <v>6406368</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2413,17 +2417,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120253384</v>
+        <v>120252861</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,33 +2436,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580279</v>
+        <v>579924</v>
       </c>
       <c r="R17" t="n">
-        <v>6406123</v>
+        <v>6406344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253032</v>
+        <v>120253744</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>96885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,38 +1185,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,13 +1225,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579906</v>
+        <v>580170</v>
       </c>
       <c r="R6" t="n">
-        <v>6406381</v>
+        <v>6406337</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,13 +1263,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253308</v>
+        <v>120253384</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,38 +1304,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1338,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580160</v>
+        <v>580279</v>
       </c>
       <c r="R7" t="n">
-        <v>6406230</v>
+        <v>6406123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1508,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253365</v>
+        <v>120252861</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,37 +1522,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1560,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580255</v>
+        <v>579924</v>
       </c>
       <c r="R9" t="n">
-        <v>6406137</v>
+        <v>6406344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,17 +1610,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253744</v>
+        <v>120253569</v>
       </c>
       <c r="B10" t="n">
-        <v>96885</v>
+        <v>91854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,35 +1633,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1675,13 +1668,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580170</v>
+        <v>579980</v>
       </c>
       <c r="R10" t="n">
-        <v>6406337</v>
+        <v>6406368</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,17 +1706,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1735,17 +1724,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253417</v>
+        <v>120253032</v>
       </c>
       <c r="B11" t="n">
-        <v>90984</v>
+        <v>90600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1743,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1793,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580291</v>
+        <v>579906</v>
       </c>
       <c r="R11" t="n">
-        <v>6406128</v>
+        <v>6406381</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,17 +1838,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253238</v>
+        <v>120252820</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,39 +1857,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1908,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580237</v>
+        <v>579928</v>
       </c>
       <c r="R12" t="n">
-        <v>6406426</v>
+        <v>6406349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1971,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253290</v>
+        <v>120253308</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,25 +1971,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2009,13 +1997,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2023,13 +2010,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580176</v>
+        <v>580160</v>
       </c>
       <c r="R13" t="n">
-        <v>6406245</v>
+        <v>6406230</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2067,6 +2054,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253384</v>
+        <v>120253417</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,35 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2133,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580279</v>
+        <v>580291</v>
       </c>
       <c r="R14" t="n">
-        <v>6406123</v>
+        <v>6406128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120252820</v>
+        <v>120253290</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,34 +2203,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2247,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579928</v>
+        <v>580176</v>
       </c>
       <c r="R15" t="n">
-        <v>6406349</v>
+        <v>6406245</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,7 +2283,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2303,17 +2294,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120253569</v>
+        <v>120253238</v>
       </c>
       <c r="B16" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,38 +2313,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2361,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579980</v>
+        <v>580237</v>
       </c>
       <c r="R16" t="n">
-        <v>6406368</v>
+        <v>6406426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,17 +2409,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120252861</v>
+        <v>120253365</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,29 +2428,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579924</v>
+        <v>580255</v>
       </c>
       <c r="R17" t="n">
-        <v>6406344</v>
+        <v>6406137</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253384</v>
+        <v>120253451</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,33 +1304,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580279</v>
+        <v>580200</v>
       </c>
       <c r="R7" t="n">
-        <v>6406123</v>
+        <v>6406118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253451</v>
+        <v>120253384</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,29 +1411,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580200</v>
+        <v>580279</v>
       </c>
       <c r="R8" t="n">
-        <v>6406118</v>
+        <v>6406123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253744</v>
+        <v>120253417</v>
       </c>
       <c r="B6" t="n">
-        <v>96885</v>
+        <v>90984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,35 +1189,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580170</v>
+        <v>580291</v>
       </c>
       <c r="R6" t="n">
-        <v>6406337</v>
+        <v>6406128</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,17 +1262,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1285,17 +1280,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253451</v>
+        <v>120253032</v>
       </c>
       <c r="B7" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,31 +1299,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1336,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580200</v>
+        <v>579906</v>
       </c>
       <c r="R7" t="n">
-        <v>6406118</v>
+        <v>6406381</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,17 +1394,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253384</v>
+        <v>120252861</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,33 +1413,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1447,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580279</v>
+        <v>579924</v>
       </c>
       <c r="R8" t="n">
-        <v>6406123</v>
+        <v>6406344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,17 +1501,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120252861</v>
+        <v>120253238</v>
       </c>
       <c r="B9" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,29 +1520,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1554,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579924</v>
+        <v>580237</v>
       </c>
       <c r="R9" t="n">
-        <v>6406344</v>
+        <v>6406426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1731,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253032</v>
+        <v>120253744</v>
       </c>
       <c r="B11" t="n">
-        <v>90600</v>
+        <v>96885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,38 +1749,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,13 +1789,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579906</v>
+        <v>580170</v>
       </c>
       <c r="R11" t="n">
-        <v>6406381</v>
+        <v>6406337</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,13 +1827,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1845,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120252820</v>
+        <v>120253384</v>
       </c>
       <c r="B12" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,38 +1868,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1896,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579928</v>
+        <v>580279</v>
       </c>
       <c r="R12" t="n">
-        <v>6406349</v>
+        <v>6406123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,17 +1960,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253308</v>
+        <v>120253451</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,34 +1983,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2010,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580160</v>
+        <v>580200</v>
       </c>
       <c r="R13" t="n">
-        <v>6406230</v>
+        <v>6406118</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253417</v>
+        <v>120253308</v>
       </c>
       <c r="B14" t="n">
-        <v>90984</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2090,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2124,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580291</v>
+        <v>580160</v>
       </c>
       <c r="R14" t="n">
-        <v>6406128</v>
+        <v>6406230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120253290</v>
+        <v>120252820</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,35 +2204,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580176</v>
+        <v>579928</v>
       </c>
       <c r="R15" t="n">
-        <v>6406245</v>
+        <v>6406349</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2283,6 +2283,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2294,14 +2295,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120253238</v>
+        <v>120253365</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2336,7 +2337,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2353,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580237</v>
+        <v>580255</v>
       </c>
       <c r="R16" t="n">
-        <v>6406426</v>
+        <v>6406137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,17 +2410,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120253365</v>
+        <v>120253290</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,39 +2429,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2468,13 +2469,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580255</v>
+        <v>580176</v>
       </c>
       <c r="R17" t="n">
-        <v>6406137</v>
+        <v>6406245</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2512,7 +2513,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42738-2024 artfynd.xlsx
+++ b/artfynd/A 42738-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253417</v>
+        <v>120253365</v>
       </c>
       <c r="B6" t="n">
-        <v>90984</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,38 +1185,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580291</v>
+        <v>580255</v>
       </c>
       <c r="R6" t="n">
-        <v>6406128</v>
+        <v>6406137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1401,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120252861</v>
+        <v>120253569</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,27 +1418,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1445,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579924</v>
+        <v>579980</v>
       </c>
       <c r="R8" t="n">
-        <v>6406344</v>
+        <v>6406368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,17 +1509,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253238</v>
+        <v>120253451</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,37 +1528,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580237</v>
+        <v>580200</v>
       </c>
       <c r="R9" t="n">
-        <v>6406426</v>
+        <v>6406118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253569</v>
+        <v>120253238</v>
       </c>
       <c r="B10" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,38 +1635,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1674,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579980</v>
+        <v>580237</v>
       </c>
       <c r="R10" t="n">
-        <v>6406368</v>
+        <v>6406426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,17 +1731,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253744</v>
+        <v>120252861</v>
       </c>
       <c r="B11" t="n">
-        <v>96885</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,33 +1754,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1789,13 +1782,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580170</v>
+        <v>579924</v>
       </c>
       <c r="R11" t="n">
-        <v>6406337</v>
+        <v>6406344</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1827,17 +1820,13 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stort område!</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1856,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253384</v>
+        <v>120252820</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,35 +1857,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1904,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580279</v>
+        <v>579928</v>
       </c>
       <c r="R12" t="n">
-        <v>6406123</v>
+        <v>6406349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,17 +1952,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120253451</v>
+        <v>120253744</v>
       </c>
       <c r="B13" t="n">
-        <v>94704</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,25 +1975,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580200</v>
+        <v>580170</v>
       </c>
       <c r="R13" t="n">
-        <v>6406118</v>
+        <v>6406337</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,13 +2049,17 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stort område!</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2067,17 +2071,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120253308</v>
+        <v>120253384</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,38 +2090,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2125,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580160</v>
+        <v>580279</v>
       </c>
       <c r="R14" t="n">
-        <v>6406230</v>
+        <v>6406123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120252820</v>
+        <v>120253308</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,30 +2201,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2239,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579928</v>
+        <v>580160</v>
       </c>
       <c r="R15" t="n">
-        <v>6406349</v>
+        <v>6406230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,17 +2296,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120253365</v>
+        <v>120253290</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,39 +2315,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2354,13 +2355,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580255</v>
+        <v>580176</v>
       </c>
       <c r="R16" t="n">
-        <v>6406137</v>
+        <v>6406245</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2398,7 +2399,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120253290</v>
+        <v>120253417</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>90984</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,25 +2429,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2455,13 +2455,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2469,13 +2468,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580176</v>
+        <v>580291</v>
       </c>
       <c r="R17" t="n">
-        <v>6406245</v>
+        <v>6406128</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2513,6 +2512,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
